--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104706_W28.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104706_W28.xlsx
@@ -565,67 +565,67 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>4.1215</v>
+        <v>4.6652</v>
       </c>
       <c r="E2" t="n">
-        <v>3.7095</v>
+        <v>3.9365</v>
       </c>
       <c r="F2" t="n">
-        <v>0.412</v>
+        <v>0.7287</v>
       </c>
       <c r="G2" t="n">
-        <v>1.5098</v>
+        <v>1.5144</v>
       </c>
       <c r="H2" t="n">
-        <v>0.3103</v>
+        <v>0.3075</v>
       </c>
       <c r="I2" t="n">
-        <v>1.1995</v>
+        <v>1.2069</v>
       </c>
       <c r="J2" t="n">
-        <v>1.5328</v>
+        <v>1.5096</v>
       </c>
       <c r="K2" t="n">
-        <v>0.4533</v>
+        <v>0.4374</v>
       </c>
       <c r="L2" t="n">
-        <v>1.0795</v>
+        <v>1.0722</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.023</v>
+        <v>0.0048</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.1431</v>
+        <v>-0.13</v>
       </c>
       <c r="O2" t="n">
-        <v>0.1201</v>
+        <v>0.1347</v>
       </c>
       <c r="P2" t="n">
-        <v>2.2683</v>
+        <v>2.2763</v>
       </c>
       <c r="Q2" t="n">
         <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>2.2683</v>
+        <v>2.2763</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.91</v>
+        <v>-0.3728</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.1693</v>
+        <v>0.0902</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.7407</v>
+        <v>-0.4629</v>
       </c>
       <c r="V2" t="n">
-        <v>1.2534</v>
+        <v>1.2472</v>
       </c>
       <c r="W2" t="n">
-        <v>2.3461</v>
+        <v>2.3367</v>
       </c>
       <c r="X2" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="3">
@@ -643,67 +643,67 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.6472</v>
+        <v>3.4435</v>
       </c>
       <c r="E3" t="n">
-        <v>3.9244</v>
+        <v>3.4434</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.2772</v>
+        <v>0.0001</v>
       </c>
       <c r="G3" t="n">
-        <v>1.4871</v>
+        <v>1.4762</v>
       </c>
       <c r="H3" t="n">
-        <v>-1.4183</v>
+        <v>-1.4269</v>
       </c>
       <c r="I3" t="n">
-        <v>2.9054</v>
+        <v>2.9032</v>
       </c>
       <c r="J3" t="n">
-        <v>2.0938</v>
+        <v>2.0639</v>
       </c>
       <c r="K3" t="n">
-        <v>-0.1425</v>
+        <v>-0.1626</v>
       </c>
       <c r="L3" t="n">
-        <v>2.2363</v>
+        <v>2.2265</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.6066</v>
+        <v>-0.5877</v>
       </c>
       <c r="N3" t="n">
-        <v>-1.2758</v>
+        <v>-1.2643</v>
       </c>
       <c r="O3" t="n">
-        <v>0.6691</v>
+        <v>0.6766</v>
       </c>
       <c r="P3" t="n">
-        <v>2.0415</v>
+        <v>2.0487</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>2.0415</v>
+        <v>2.0487</v>
       </c>
       <c r="S3" t="n">
-        <v>0.1186</v>
+        <v>-0.0814</v>
       </c>
       <c r="T3" t="n">
-        <v>0.738</v>
+        <v>0.29</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.6194</v>
+        <v>-0.3714</v>
       </c>
       <c r="V3" t="n">
         <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="X3" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="4">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.0958</v>
+        <v>2.5581</v>
       </c>
       <c r="E4" t="n">
-        <v>3.22</v>
+        <v>3.6295</v>
       </c>
       <c r="F4" t="n">
-        <v>-1.1242</v>
+        <v>-1.0714</v>
       </c>
       <c r="G4" t="n">
-        <v>2.5517</v>
+        <v>2.5559</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.7029</v>
+        <v>-0.6927</v>
       </c>
       <c r="I4" t="n">
-        <v>3.2546</v>
+        <v>3.2486</v>
       </c>
       <c r="J4" t="n">
-        <v>3.846</v>
+        <v>3.8318</v>
       </c>
       <c r="K4" t="n">
-        <v>0.4156</v>
+        <v>0.4137</v>
       </c>
       <c r="L4" t="n">
-        <v>3.4304</v>
+        <v>3.4181</v>
       </c>
       <c r="M4" t="n">
-        <v>-1.2944</v>
+        <v>-1.2759</v>
       </c>
       <c r="N4" t="n">
-        <v>-1.1185</v>
+        <v>-1.1064</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.1759</v>
+        <v>-0.1695</v>
       </c>
       <c r="P4" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="S4" t="n">
-        <v>-1.0437</v>
+        <v>-0.5911</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.6261</v>
+        <v>-0.2023</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.4177</v>
+        <v>-0.3888</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.5463</v>
+        <v>-0.5447</v>
       </c>
       <c r="W4" t="n">
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.5463</v>
+        <v>-0.5447</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>D. BRANKOVIC</t>
+          <t>D. MAVRA</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,64 +799,64 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.0643</v>
+        <v>0.8294</v>
       </c>
       <c r="E5" t="n">
-        <v>0.1498</v>
+        <v>0.6274</v>
       </c>
       <c r="F5" t="n">
-        <v>0.9145</v>
+        <v>0.202</v>
       </c>
       <c r="G5" t="n">
-        <v>1.1359</v>
+        <v>6.1871</v>
       </c>
       <c r="H5" t="n">
-        <v>2.0448</v>
+        <v>4.4061</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.9089</v>
+        <v>1.781</v>
       </c>
       <c r="J5" t="n">
-        <v>1.2926</v>
+        <v>7.0285</v>
       </c>
       <c r="K5" t="n">
-        <v>1.967</v>
+        <v>4.3782</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.6744</v>
+        <v>2.6504</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.1567</v>
+        <v>-0.8414</v>
       </c>
       <c r="N5" t="n">
-        <v>0.07779999999999999</v>
+        <v>0.028</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.2345</v>
+        <v>-0.8694</v>
       </c>
       <c r="P5" t="n">
-        <v>-1.361</v>
+        <v>-4.325</v>
       </c>
       <c r="Q5" t="n">
-        <v>-2.2683</v>
+        <v>-5.6908</v>
       </c>
       <c r="R5" t="n">
-        <v>0.9073</v>
+        <v>1.3658</v>
       </c>
       <c r="S5" t="n">
-        <v>1.1287</v>
+        <v>-0.8035</v>
       </c>
       <c r="T5" t="n">
-        <v>0.9648</v>
+        <v>-0.4811</v>
       </c>
       <c r="U5" t="n">
-        <v>0.1639</v>
+        <v>-0.3224</v>
       </c>
       <c r="V5" t="n">
-        <v>0.1607</v>
+        <v>-0.2292</v>
       </c>
       <c r="W5" t="n">
-        <v>0.1607</v>
+        <v>-0.2292</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>D. APIC</t>
+          <t>E. QUINTELA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.4787</v>
+        <v>0.5884</v>
       </c>
       <c r="E6" t="n">
-        <v>0.9396</v>
+        <v>0.2133</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.4609</v>
+        <v>0.3751</v>
       </c>
       <c r="G6" t="n">
-        <v>0.7542</v>
+        <v>1.1423</v>
       </c>
       <c r="H6" t="n">
-        <v>0.5223</v>
+        <v>0.1356</v>
       </c>
       <c r="I6" t="n">
-        <v>0.2319</v>
+        <v>1.0067</v>
       </c>
       <c r="J6" t="n">
-        <v>1.1483</v>
+        <v>1.6722</v>
       </c>
       <c r="K6" t="n">
-        <v>1.0736</v>
+        <v>0.8683</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0746</v>
+        <v>0.8038999999999999</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.394</v>
+        <v>-0.53</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.5513</v>
+        <v>-0.7328</v>
       </c>
       <c r="O6" t="n">
-        <v>0.1573</v>
+        <v>0.2028</v>
       </c>
       <c r="P6" t="n">
-        <v>0.2268</v>
+        <v>0.4553</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>-1.1382</v>
       </c>
       <c r="R6" t="n">
-        <v>0.2268</v>
+        <v>1.5934</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.5024</v>
+        <v>-0.3066</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.2087</v>
+        <v>-0.3207</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.2937</v>
+        <v>0.0141</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>-0.7025</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>-0.7025</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>D. MAVRA</t>
+          <t>D. APIC</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,64 +955,64 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.4553</v>
+        <v>0.51</v>
       </c>
       <c r="E7" t="n">
-        <v>0.344</v>
+        <v>0.9340000000000001</v>
       </c>
       <c r="F7" t="n">
-        <v>0.1113</v>
+        <v>-0.424</v>
       </c>
       <c r="G7" t="n">
-        <v>6.2065</v>
+        <v>0.7551</v>
       </c>
       <c r="H7" t="n">
-        <v>4.4127</v>
+        <v>0.5227000000000001</v>
       </c>
       <c r="I7" t="n">
-        <v>1.7938</v>
+        <v>0.2324</v>
       </c>
       <c r="J7" t="n">
-        <v>7.0744</v>
+        <v>1.1432</v>
       </c>
       <c r="K7" t="n">
-        <v>4.3985</v>
+        <v>1.0687</v>
       </c>
       <c r="L7" t="n">
-        <v>2.676</v>
+        <v>0.0745</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.868</v>
+        <v>-0.3881</v>
       </c>
       <c r="N7" t="n">
-        <v>0.0142</v>
+        <v>-0.546</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.8822</v>
+        <v>0.1579</v>
       </c>
       <c r="P7" t="n">
-        <v>-4.3098</v>
+        <v>0.2276</v>
       </c>
       <c r="Q7" t="n">
-        <v>-5.6708</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1.361</v>
+        <v>0.2276</v>
       </c>
       <c r="S7" t="n">
-        <v>-1.2164</v>
+        <v>-0.4727</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.8347</v>
+        <v>-0.2091</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.3817</v>
+        <v>-0.2636</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.2249</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>-0.2249</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
         <v>0</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>E. QUINTELA</t>
+          <t>A. ARANITOVIC</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.4196</v>
+        <v>0.3334</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.0584</v>
+        <v>1.221</v>
       </c>
       <c r="F8" t="n">
-        <v>0.478</v>
+        <v>-0.8875</v>
       </c>
       <c r="G8" t="n">
-        <v>1.1588</v>
+        <v>0.7422</v>
       </c>
       <c r="H8" t="n">
-        <v>0.1459</v>
+        <v>0.7692</v>
       </c>
       <c r="I8" t="n">
-        <v>1.0129</v>
+        <v>-0.0269</v>
       </c>
       <c r="J8" t="n">
-        <v>1.7018</v>
+        <v>1.4257</v>
       </c>
       <c r="K8" t="n">
-        <v>0.8863</v>
+        <v>0.7412</v>
       </c>
       <c r="L8" t="n">
-        <v>0.8156</v>
+        <v>0.6845</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.5431</v>
+        <v>-0.6835</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.7403999999999999</v>
+        <v>0.028</v>
       </c>
       <c r="O8" t="n">
-        <v>0.1973</v>
+        <v>-0.7114</v>
       </c>
       <c r="P8" t="n">
-        <v>0.4537</v>
+        <v>1.3658</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.1342</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1.5878</v>
+        <v>1.3658</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.4857</v>
+        <v>-0.6851</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.6261</v>
+        <v>-0.2047</v>
       </c>
       <c r="U8" t="n">
-        <v>0.1403</v>
+        <v>-0.4804</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.7071</v>
+        <v>-1.0895</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.7071</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A. ARANITOVIC</t>
+          <t>D. BRANKOVIC</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.2829</v>
+        <v>0.3057</v>
       </c>
       <c r="E9" t="n">
-        <v>0.6985</v>
+        <v>-0.5647</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.9814000000000001</v>
+        <v>0.8704</v>
       </c>
       <c r="G9" t="n">
-        <v>0.7348</v>
+        <v>1.1328</v>
       </c>
       <c r="H9" t="n">
-        <v>0.7588</v>
+        <v>2.0367</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.024</v>
+        <v>-0.904</v>
       </c>
       <c r="J9" t="n">
-        <v>1.4455</v>
+        <v>1.2731</v>
       </c>
       <c r="K9" t="n">
-        <v>0.7446</v>
+        <v>1.951</v>
       </c>
       <c r="L9" t="n">
-        <v>0.7009</v>
+        <v>-0.6778999999999999</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.7107</v>
+        <v>-0.1403</v>
       </c>
       <c r="N9" t="n">
-        <v>0.0142</v>
+        <v>0.0857</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.7249</v>
+        <v>-0.226</v>
       </c>
       <c r="P9" t="n">
-        <v>1.361</v>
+        <v>-1.3658</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>-2.2763</v>
       </c>
       <c r="R9" t="n">
-        <v>1.361</v>
+        <v>0.9105</v>
       </c>
       <c r="S9" t="n">
-        <v>-1.286</v>
+        <v>0.3809</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.747</v>
+        <v>0.2808</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.539</v>
+        <v>0.1002</v>
       </c>
       <c r="V9" t="n">
-        <v>-1.0927</v>
+        <v>0.1578</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>0.1578</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.0927</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>J. SAKHO</t>
+          <t>A. KURUCS</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.5037</v>
+        <v>-0.8721</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.4276</v>
+        <v>-2.6254</v>
       </c>
       <c r="F10" t="n">
-        <v>0.9239000000000001</v>
+        <v>1.7533</v>
       </c>
       <c r="G10" t="n">
-        <v>-1.0813</v>
+        <v>-0.5701000000000001</v>
       </c>
       <c r="H10" t="n">
-        <v>-1.4012</v>
+        <v>-2.5706</v>
       </c>
       <c r="I10" t="n">
-        <v>0.32</v>
+        <v>2.0005</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.3147</v>
+        <v>-0.3837</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.6132</v>
+        <v>-1.4931</v>
       </c>
       <c r="L10" t="n">
-        <v>0.2985</v>
+        <v>1.1094</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.7665999999999999</v>
+        <v>-0.1865</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.788</v>
+        <v>-1.0775</v>
       </c>
       <c r="O10" t="n">
-        <v>0.0214</v>
+        <v>0.8911</v>
       </c>
       <c r="P10" t="n">
-        <v>1.1342</v>
+        <v>-0.4553</v>
       </c>
       <c r="Q10" t="n">
-        <v>-1.1342</v>
+        <v>-2.2763</v>
       </c>
       <c r="R10" t="n">
-        <v>2.2683</v>
+        <v>1.8211</v>
       </c>
       <c r="S10" t="n">
-        <v>0.6968</v>
+        <v>0.1533</v>
       </c>
       <c r="T10" t="n">
-        <v>0.0212</v>
+        <v>0.0346</v>
       </c>
       <c r="U10" t="n">
-        <v>0.6756</v>
+        <v>0.1187</v>
       </c>
       <c r="V10" t="n">
-        <v>-1.2534</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.2534</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>F. ALONSO</t>
+          <t>J. SAKHO</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1267,73 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.886</v>
+        <v>-1.0387</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.1005</v>
+        <v>-1.2465</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.7855</v>
+        <v>0.2078</v>
       </c>
       <c r="G11" t="n">
-        <v>-1.6046</v>
+        <v>-1.0622</v>
       </c>
       <c r="H11" t="n">
-        <v>0.08799999999999999</v>
+        <v>-1.3934</v>
       </c>
       <c r="I11" t="n">
-        <v>-1.6926</v>
+        <v>0.3312</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.4889</v>
+        <v>-0.3194</v>
       </c>
       <c r="K11" t="n">
-        <v>0.2629</v>
+        <v>-0.6173</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.7517</v>
+        <v>0.2979</v>
       </c>
       <c r="M11" t="n">
-        <v>-1.1157</v>
+        <v>-0.7428</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.1749</v>
+        <v>-0.7761</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.9408</v>
+        <v>0.0333</v>
       </c>
       <c r="P11" t="n">
-        <v>-0.6805</v>
+        <v>1.1382</v>
       </c>
       <c r="Q11" t="n">
-        <v>-2.2683</v>
+        <v>-1.1382</v>
       </c>
       <c r="R11" t="n">
-        <v>1.5878</v>
+        <v>2.2763</v>
       </c>
       <c r="S11" t="n">
-        <v>0.3064</v>
+        <v>0.1326</v>
       </c>
       <c r="T11" t="n">
-        <v>1.4034</v>
+        <v>0.2111</v>
       </c>
       <c r="U11" t="n">
-        <v>-1.097</v>
+        <v>-0.0785</v>
       </c>
       <c r="V11" t="n">
-        <v>1.0927</v>
+        <v>-1.2472</v>
       </c>
       <c r="W11" t="n">
-        <v>1.2534</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-0.1607</v>
+        <v>-1.2472</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A. KURUCS</t>
+          <t>F. ALONSO</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-1.4687</v>
+        <v>-1.8256</v>
       </c>
       <c r="E12" t="n">
-        <v>-3.2637</v>
+        <v>-1.2932</v>
       </c>
       <c r="F12" t="n">
-        <v>1.795</v>
+        <v>-0.5324</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.571</v>
+        <v>-1.597</v>
       </c>
       <c r="H12" t="n">
-        <v>-2.5728</v>
+        <v>0.089</v>
       </c>
       <c r="I12" t="n">
-        <v>2.0018</v>
+        <v>-1.686</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.3693</v>
+        <v>-0.5123</v>
       </c>
       <c r="K12" t="n">
-        <v>-1.4861</v>
+        <v>0.2478</v>
       </c>
       <c r="L12" t="n">
-        <v>1.1168</v>
+        <v>-0.7601</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.2017</v>
+        <v>-1.0847</v>
       </c>
       <c r="N12" t="n">
-        <v>-1.0867</v>
+        <v>-0.1588</v>
       </c>
       <c r="O12" t="n">
-        <v>0.885</v>
+        <v>-0.9258999999999999</v>
       </c>
       <c r="P12" t="n">
-        <v>-0.4537</v>
+        <v>-0.6829</v>
       </c>
       <c r="Q12" t="n">
-        <v>-2.2683</v>
+        <v>-2.2763</v>
       </c>
       <c r="R12" t="n">
-        <v>1.8147</v>
+        <v>1.5934</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.444</v>
+        <v>-0.6352</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.6261</v>
+        <v>0.2481</v>
       </c>
       <c r="U12" t="n">
-        <v>0.1821</v>
+        <v>-0.8834</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>1.0895</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>1.2472</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="13">
@@ -1423,67 +1423,67 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-5.3584</v>
+        <v>-4.6858</v>
       </c>
       <c r="E13" t="n">
-        <v>-3.2903</v>
+        <v>-2.693</v>
       </c>
       <c r="F13" t="n">
-        <v>-2.0681</v>
+        <v>-1.9927</v>
       </c>
       <c r="G13" t="n">
-        <v>-0.8073</v>
+        <v>-0.8089</v>
       </c>
       <c r="H13" t="n">
-        <v>-0.5354</v>
+        <v>-0.5315</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.2719</v>
+        <v>-0.2773</v>
       </c>
       <c r="J13" t="n">
-        <v>-0.901</v>
+        <v>-0.909</v>
       </c>
       <c r="K13" t="n">
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>-0.901</v>
+        <v>-0.909</v>
       </c>
       <c r="M13" t="n">
-        <v>0.09370000000000001</v>
+        <v>0.1002</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.5354</v>
+        <v>-0.5315</v>
       </c>
       <c r="O13" t="n">
-        <v>0.6291</v>
+        <v>0.6317</v>
       </c>
       <c r="P13" t="n">
-        <v>-1.8147</v>
+        <v>-1.8211</v>
       </c>
       <c r="Q13" t="n">
-        <v>-2.2683</v>
+        <v>-2.2763</v>
       </c>
       <c r="R13" t="n">
-        <v>0.4537</v>
+        <v>0.4553</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.5511</v>
+        <v>0.1231</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.121</v>
+        <v>0.4923</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.4301</v>
+        <v>-0.3692</v>
       </c>
       <c r="V13" t="n">
-        <v>-2.1853</v>
+        <v>-2.1789</v>
       </c>
       <c r="W13" t="n">
         <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>-2.1853</v>
+        <v>-2.1789</v>
       </c>
     </row>
     <row r="14">
@@ -1501,67 +1501,67 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>3.782700000000002</v>
+        <v>4.811499999999999</v>
       </c>
       <c r="E14" t="n">
-        <v>4.8453</v>
+        <v>5.582300000000002</v>
       </c>
       <c r="F14" t="n">
-        <v>-1.0626</v>
+        <v>-0.7705999999999997</v>
       </c>
       <c r="G14" t="n">
-        <v>11.4746</v>
+        <v>11.4678</v>
       </c>
       <c r="H14" t="n">
-        <v>1.652200000000001</v>
+        <v>1.651700000000001</v>
       </c>
       <c r="I14" t="n">
-        <v>9.822499999999998</v>
+        <v>9.816300000000002</v>
       </c>
       <c r="J14" t="n">
-        <v>18.0613</v>
+        <v>17.8236</v>
       </c>
       <c r="K14" t="n">
-        <v>7.959999999999999</v>
+        <v>7.833299999999999</v>
       </c>
       <c r="L14" t="n">
-        <v>10.1015</v>
+        <v>9.990399999999999</v>
       </c>
       <c r="M14" t="n">
-        <v>-6.586800000000001</v>
+        <v>-6.355899999999999</v>
       </c>
       <c r="N14" t="n">
-        <v>-6.307900000000001</v>
+        <v>-6.181699999999999</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.2789999999999999</v>
+        <v>-0.1740999999999999</v>
       </c>
       <c r="P14" t="n">
-        <v>2.220446049250313e-16</v>
+        <v>4.440892098500626e-16</v>
       </c>
       <c r="Q14" t="n">
-        <v>-17.0124</v>
+        <v>-17.0724</v>
       </c>
       <c r="R14" t="n">
-        <v>17.0124</v>
+        <v>17.0724</v>
       </c>
       <c r="S14" t="n">
-        <v>-4.188800000000001</v>
+        <v>-3.1585</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.8316</v>
+        <v>0.2291999999999999</v>
       </c>
       <c r="U14" t="n">
-        <v>-3.3574</v>
+        <v>-3.3876</v>
       </c>
       <c r="V14" t="n">
-        <v>-3.502899999999999</v>
+        <v>-3.4975</v>
       </c>
       <c r="W14" t="n">
-        <v>4.628</v>
+        <v>4.601999999999999</v>
       </c>
       <c r="X14" t="n">
-        <v>-8.1309</v>
+        <v>-8.099600000000001</v>
       </c>
     </row>
     <row r="15">
@@ -1579,64 +1579,64 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>3.951</v>
+        <v>3.8415</v>
       </c>
       <c r="E15" t="n">
-        <v>4.9274</v>
+        <v>4.6823</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.9764</v>
+        <v>-0.8408</v>
       </c>
       <c r="G15" t="n">
-        <v>1.9008</v>
+        <v>1.902</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.5195</v>
+        <v>-0.5171</v>
       </c>
       <c r="I15" t="n">
-        <v>2.4203</v>
+        <v>2.4191</v>
       </c>
       <c r="J15" t="n">
-        <v>3.257</v>
+        <v>3.2492</v>
       </c>
       <c r="K15" t="n">
-        <v>0.3463</v>
+        <v>0.3447</v>
       </c>
       <c r="L15" t="n">
-        <v>2.9107</v>
+        <v>2.9045</v>
       </c>
       <c r="M15" t="n">
-        <v>-1.3563</v>
+        <v>-1.3472</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.8658</v>
+        <v>-0.8618</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.4904</v>
+        <v>-0.4854</v>
       </c>
       <c r="P15" t="n">
-        <v>0.4537</v>
+        <v>0.4553</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>0.4537</v>
+        <v>0.4553</v>
       </c>
       <c r="S15" t="n">
-        <v>0.5039</v>
+        <v>0.3948</v>
       </c>
       <c r="T15" t="n">
-        <v>0.5777</v>
+        <v>0.3436</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.0738</v>
+        <v>0.0512</v>
       </c>
       <c r="V15" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="W15" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="X15" t="n">
         <v>0</v>
@@ -1657,67 +1657,67 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.998</v>
+        <v>2.5237</v>
       </c>
       <c r="E16" t="n">
-        <v>2.2186</v>
+        <v>2.8589</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.2206</v>
+        <v>-0.3352</v>
       </c>
       <c r="G16" t="n">
-        <v>0.6289</v>
+        <v>0.6142</v>
       </c>
       <c r="H16" t="n">
-        <v>0.0159</v>
+        <v>0.0144</v>
       </c>
       <c r="I16" t="n">
-        <v>0.613</v>
+        <v>0.5997</v>
       </c>
       <c r="J16" t="n">
-        <v>3.9113</v>
+        <v>3.8662</v>
       </c>
       <c r="K16" t="n">
-        <v>1.198</v>
+        <v>1.1786</v>
       </c>
       <c r="L16" t="n">
-        <v>2.7133</v>
+        <v>2.6876</v>
       </c>
       <c r="M16" t="n">
-        <v>-3.2824</v>
+        <v>-3.2521</v>
       </c>
       <c r="N16" t="n">
-        <v>-1.1821</v>
+        <v>-1.1642</v>
       </c>
       <c r="O16" t="n">
-        <v>-2.1003</v>
+        <v>-2.0879</v>
       </c>
       <c r="P16" t="n">
-        <v>-0.9073</v>
+        <v>-0.9105</v>
       </c>
       <c r="Q16" t="n">
-        <v>-3.4025</v>
+        <v>-3.4145</v>
       </c>
       <c r="R16" t="n">
-        <v>2.4952</v>
+        <v>2.5039</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.4552</v>
+        <v>0.0964</v>
       </c>
       <c r="T16" t="n">
-        <v>-1.1825</v>
+        <v>-0.4743</v>
       </c>
       <c r="U16" t="n">
-        <v>0.7274</v>
+        <v>0.5707</v>
       </c>
       <c r="V16" t="n">
-        <v>2.7317</v>
+        <v>2.7237</v>
       </c>
       <c r="W16" t="n">
-        <v>2.8924</v>
+        <v>2.8814</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.1607</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="17">
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.2321</v>
+        <v>2.3185</v>
       </c>
       <c r="E17" t="n">
-        <v>2.3543</v>
+        <v>3.0156</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.1222</v>
+        <v>-0.6971000000000001</v>
       </c>
       <c r="G17" t="n">
-        <v>-1.0762</v>
+        <v>-1.0752</v>
       </c>
       <c r="H17" t="n">
-        <v>3.0634</v>
+        <v>3.0645</v>
       </c>
       <c r="I17" t="n">
         <v>-4.1396</v>
       </c>
       <c r="J17" t="n">
-        <v>1.3798</v>
+        <v>1.3423</v>
       </c>
       <c r="K17" t="n">
-        <v>3.9309</v>
+        <v>3.9128</v>
       </c>
       <c r="L17" t="n">
-        <v>-2.5511</v>
+        <v>-2.5704</v>
       </c>
       <c r="M17" t="n">
-        <v>-2.456</v>
+        <v>-2.4175</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.8675</v>
+        <v>-0.8483000000000001</v>
       </c>
       <c r="O17" t="n">
-        <v>-1.5885</v>
+        <v>-1.5692</v>
       </c>
       <c r="P17" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="Q17" t="n">
-        <v>-1.361</v>
+        <v>-1.3658</v>
       </c>
       <c r="R17" t="n">
-        <v>2.9488</v>
+        <v>2.9592</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.9185</v>
+        <v>0.1661</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.3962</v>
+        <v>0.3154</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.5223</v>
+        <v>-0.1493</v>
       </c>
       <c r="V17" t="n">
-        <v>1.639</v>
+        <v>1.6342</v>
       </c>
       <c r="W17" t="n">
-        <v>2.7317</v>
+        <v>2.7237</v>
       </c>
       <c r="X17" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="18">
@@ -1813,58 +1813,58 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.8549</v>
+        <v>1.1386</v>
       </c>
       <c r="E18" t="n">
-        <v>0.0276</v>
+        <v>0.1349</v>
       </c>
       <c r="F18" t="n">
-        <v>0.8274</v>
+        <v>1.0037</v>
       </c>
       <c r="G18" t="n">
-        <v>0.2969</v>
+        <v>0.3035</v>
       </c>
       <c r="H18" t="n">
-        <v>1.3391</v>
+        <v>1.3384</v>
       </c>
       <c r="I18" t="n">
-        <v>-1.0422</v>
+        <v>-1.035</v>
       </c>
       <c r="J18" t="n">
-        <v>0.6536</v>
+        <v>0.6438</v>
       </c>
       <c r="K18" t="n">
-        <v>0.6163</v>
+        <v>0.6065</v>
       </c>
       <c r="L18" t="n">
-        <v>0.0373</v>
+        <v>0.0372</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.3567</v>
+        <v>-0.3403</v>
       </c>
       <c r="N18" t="n">
-        <v>0.7228</v>
+        <v>0.7319</v>
       </c>
       <c r="O18" t="n">
-        <v>-1.0795</v>
+        <v>-1.0722</v>
       </c>
       <c r="P18" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.5762</v>
+        <v>-0.3031</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.6261</v>
+        <v>-0.5089</v>
       </c>
       <c r="U18" t="n">
-        <v>0.0499</v>
+        <v>0.2058</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Y. KRAAG</t>
+          <t>M. RUZIC</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.6415</v>
+        <v>0.4756</v>
       </c>
       <c r="E19" t="n">
-        <v>1.2345</v>
+        <v>-0.987</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.5931</v>
+        <v>1.4626</v>
       </c>
       <c r="G19" t="n">
-        <v>-1.1693</v>
+        <v>-0.4054</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.0738</v>
+        <v>-0.0317</v>
       </c>
       <c r="I19" t="n">
-        <v>-1.0955</v>
+        <v>-0.3737</v>
       </c>
       <c r="J19" t="n">
-        <v>1.7668</v>
+        <v>-0.2782</v>
       </c>
       <c r="K19" t="n">
-        <v>0.7619</v>
+        <v>0.3997</v>
       </c>
       <c r="L19" t="n">
-        <v>1.0048</v>
+        <v>-0.6778999999999999</v>
       </c>
       <c r="M19" t="n">
-        <v>-2.9361</v>
+        <v>-0.1271</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.8357</v>
+        <v>-0.4314</v>
       </c>
       <c r="O19" t="n">
-        <v>-2.1003</v>
+        <v>0.3043</v>
       </c>
       <c r="P19" t="n">
-        <v>-1.8147</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>-3.6293</v>
+        <v>-1.3658</v>
       </c>
       <c r="R19" t="n">
-        <v>1.8147</v>
+        <v>1.3658</v>
       </c>
       <c r="S19" t="n">
-        <v>3.6254</v>
+        <v>0.8095</v>
       </c>
       <c r="T19" t="n">
-        <v>3.0971</v>
+        <v>0.6571</v>
       </c>
       <c r="U19" t="n">
-        <v>0.5283</v>
+        <v>0.1524</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>0.07140000000000001</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>0.07140000000000001</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>M. RUZIC</t>
+          <t>A. HANGA</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.0206</v>
+        <v>0.3148</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.3275</v>
+        <v>1.0206</v>
       </c>
       <c r="F20" t="n">
-        <v>1.3069</v>
+        <v>-0.7059</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.4117</v>
+        <v>-1.0361</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.0332</v>
+        <v>-1.4996</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.3785</v>
+        <v>0.4635</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.2659</v>
+        <v>0.712</v>
       </c>
       <c r="K20" t="n">
-        <v>0.4085</v>
+        <v>0.1239</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.6744</v>
+        <v>0.5881</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.1458</v>
+        <v>-1.7481</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.4417</v>
+        <v>-1.6235</v>
       </c>
       <c r="O20" t="n">
-        <v>0.2959</v>
+        <v>-0.1246</v>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>0.4553</v>
       </c>
       <c r="Q20" t="n">
-        <v>-1.361</v>
+        <v>-1.1382</v>
       </c>
       <c r="R20" t="n">
-        <v>1.361</v>
+        <v>1.5934</v>
       </c>
       <c r="S20" t="n">
-        <v>0.3269</v>
+        <v>0.5086000000000001</v>
       </c>
       <c r="T20" t="n">
-        <v>0.2994</v>
+        <v>0.3573</v>
       </c>
       <c r="U20" t="n">
-        <v>0.0275</v>
+        <v>0.1513</v>
       </c>
       <c r="V20" t="n">
-        <v>0.06419999999999999</v>
+        <v>0.387</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>1.0895</v>
       </c>
       <c r="X20" t="n">
-        <v>0.06419999999999999</v>
+        <v>-0.7025</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A. HANGA</t>
+          <t>Y. KRAAG</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.3939</v>
+        <v>-1.6843</v>
       </c>
       <c r="E21" t="n">
-        <v>0.5664</v>
+        <v>-0.9062</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.9602000000000001</v>
+        <v>-0.7781</v>
       </c>
       <c r="G21" t="n">
-        <v>-1.048</v>
+        <v>-1.1512</v>
       </c>
       <c r="H21" t="n">
-        <v>-1.5066</v>
+        <v>-0.061</v>
       </c>
       <c r="I21" t="n">
-        <v>0.4585</v>
+        <v>-1.0902</v>
       </c>
       <c r="J21" t="n">
-        <v>0.7258</v>
+        <v>1.7561</v>
       </c>
       <c r="K21" t="n">
-        <v>0.1314</v>
+        <v>0.7584</v>
       </c>
       <c r="L21" t="n">
-        <v>0.5944</v>
+        <v>0.9977</v>
       </c>
       <c r="M21" t="n">
-        <v>-1.7738</v>
+        <v>-2.9073</v>
       </c>
       <c r="N21" t="n">
-        <v>-1.638</v>
+        <v>-0.8194</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.1359</v>
+        <v>-2.0879</v>
       </c>
       <c r="P21" t="n">
-        <v>0.4537</v>
+        <v>-1.8211</v>
       </c>
       <c r="Q21" t="n">
-        <v>-1.1342</v>
+        <v>-3.6421</v>
       </c>
       <c r="R21" t="n">
-        <v>1.5878</v>
+        <v>1.8211</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.1851</v>
+        <v>1.2879</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.1179</v>
+        <v>0.9797</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.0672</v>
+        <v>0.3082</v>
       </c>
       <c r="V21" t="n">
-        <v>0.3856</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>1.0927</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-0.7071</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>H. DRELL</t>
+          <t>L. HAKANSON</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.0361</v>
+        <v>-1.7112</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.2346</v>
+        <v>-2.4819</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.8015</v>
+        <v>0.7707000000000001</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.4073</v>
+        <v>-1.3964</v>
       </c>
       <c r="H22" t="n">
-        <v>1.0694</v>
+        <v>0.2381</v>
       </c>
       <c r="I22" t="n">
-        <v>-1.4767</v>
+        <v>-1.6345</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.0506</v>
+        <v>-0.7534</v>
       </c>
       <c r="K22" t="n">
-        <v>0.6611</v>
+        <v>0.655</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.7117</v>
+        <v>-1.4084</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.3567</v>
+        <v>-0.643</v>
       </c>
       <c r="N22" t="n">
-        <v>0.4082</v>
+        <v>-0.4169</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.7649</v>
+        <v>-0.226</v>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>-1.1382</v>
       </c>
       <c r="Q22" t="n">
-        <v>-1.361</v>
+        <v>-2.5039</v>
       </c>
       <c r="R22" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="S22" t="n">
-        <v>1.3958</v>
+        <v>0.8234</v>
       </c>
       <c r="T22" t="n">
-        <v>1.0162</v>
+        <v>0.7755</v>
       </c>
       <c r="U22" t="n">
-        <v>0.3796</v>
+        <v>0.0479</v>
       </c>
       <c r="V22" t="n">
-        <v>-2.0246</v>
+        <v>0</v>
       </c>
       <c r="W22" t="n">
-        <v>0.1607</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>-2.1853</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>S. BIRGANDER</t>
+          <t>H. DRELL</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,73 +2203,73 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-1.7819</v>
+        <v>-1.7413</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.3128</v>
+        <v>-0.9679</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.4691</v>
+        <v>-0.7734</v>
       </c>
       <c r="G23" t="n">
-        <v>-2.688</v>
+        <v>-0.4112</v>
       </c>
       <c r="H23" t="n">
-        <v>-1.9364</v>
+        <v>1.0603</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.7516</v>
+        <v>-1.4715</v>
       </c>
       <c r="J23" t="n">
-        <v>-0.6122</v>
+        <v>-0.0709</v>
       </c>
       <c r="K23" t="n">
-        <v>-0.7242</v>
+        <v>0.6443</v>
       </c>
       <c r="L23" t="n">
-        <v>0.112</v>
+        <v>-0.7151999999999999</v>
       </c>
       <c r="M23" t="n">
-        <v>-2.0758</v>
+        <v>-0.3403</v>
       </c>
       <c r="N23" t="n">
-        <v>-1.2122</v>
+        <v>0.416</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.8636</v>
+        <v>-0.7563</v>
       </c>
       <c r="P23" t="n">
-        <v>0.6805</v>
+        <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>-1.3658</v>
       </c>
       <c r="R23" t="n">
-        <v>0.6805</v>
+        <v>1.3658</v>
       </c>
       <c r="S23" t="n">
-        <v>0.2256</v>
+        <v>0.6911</v>
       </c>
       <c r="T23" t="n">
-        <v>0.2994</v>
+        <v>0.311</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.0738</v>
+        <v>0.3801</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>-2.0212</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>0.1578</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>-2.1789</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>L. HAKANSON</t>
+          <t>S. BIRGANDER</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,58 +2281,58 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-2.2428</v>
+        <v>-1.77</v>
       </c>
       <c r="E24" t="n">
-        <v>-2.9292</v>
+        <v>-0.4397</v>
       </c>
       <c r="F24" t="n">
-        <v>0.6865</v>
+        <v>-1.3303</v>
       </c>
       <c r="G24" t="n">
-        <v>-1.3938</v>
+        <v>-2.6873</v>
       </c>
       <c r="H24" t="n">
-        <v>0.2322</v>
+        <v>-1.9413</v>
       </c>
       <c r="I24" t="n">
-        <v>-1.626</v>
+        <v>-0.746</v>
       </c>
       <c r="J24" t="n">
-        <v>-0.7335</v>
+        <v>-0.623</v>
       </c>
       <c r="K24" t="n">
-        <v>0.658</v>
+        <v>-0.7347</v>
       </c>
       <c r="L24" t="n">
-        <v>-1.3915</v>
+        <v>0.1117</v>
       </c>
       <c r="M24" t="n">
-        <v>-0.6603</v>
+        <v>-2.0643</v>
       </c>
       <c r="N24" t="n">
-        <v>-0.4258</v>
+        <v>-1.2066</v>
       </c>
       <c r="O24" t="n">
-        <v>-0.2345</v>
+        <v>-0.8578</v>
       </c>
       <c r="P24" t="n">
-        <v>-1.1342</v>
+        <v>0.6829</v>
       </c>
       <c r="Q24" t="n">
-        <v>-2.4952</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>1.361</v>
+        <v>0.6829</v>
       </c>
       <c r="S24" t="n">
-        <v>0.2852</v>
+        <v>0.2345</v>
       </c>
       <c r="T24" t="n">
-        <v>0.2994</v>
+        <v>0.1833</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.0142</v>
+        <v>0.0512</v>
       </c>
       <c r="V24" t="n">
         <v>0</v>
@@ -2359,67 +2359,67 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-6.9852</v>
+        <v>-6.6823</v>
       </c>
       <c r="E25" t="n">
-        <v>-4.3695</v>
+        <v>-4.0693</v>
       </c>
       <c r="F25" t="n">
-        <v>-2.6157</v>
+        <v>-2.6129</v>
       </c>
       <c r="G25" t="n">
-        <v>-6.1069</v>
+        <v>-6.1246</v>
       </c>
       <c r="H25" t="n">
-        <v>-3.3027</v>
+        <v>-3.3165</v>
       </c>
       <c r="I25" t="n">
-        <v>-2.8042</v>
+        <v>-2.8081</v>
       </c>
       <c r="J25" t="n">
-        <v>-3.4453</v>
+        <v>-3.4882</v>
       </c>
       <c r="K25" t="n">
-        <v>-1.6806</v>
+        <v>-1.7074</v>
       </c>
       <c r="L25" t="n">
-        <v>-1.7647</v>
+        <v>-1.7808</v>
       </c>
       <c r="M25" t="n">
-        <v>-2.6615</v>
+        <v>-2.6364</v>
       </c>
       <c r="N25" t="n">
-        <v>-1.6221</v>
+        <v>-1.6091</v>
       </c>
       <c r="O25" t="n">
-        <v>-1.0395</v>
+        <v>-1.0273</v>
       </c>
       <c r="P25" t="n">
-        <v>-0.4537</v>
+        <v>-0.4553</v>
       </c>
       <c r="Q25" t="n">
-        <v>-2.2683</v>
+        <v>-2.2763</v>
       </c>
       <c r="R25" t="n">
-        <v>1.8147</v>
+        <v>1.8211</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.039</v>
+        <v>0.2845</v>
       </c>
       <c r="T25" t="n">
-        <v>0.0907</v>
+        <v>0.448</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.1298</v>
+        <v>-0.1634</v>
       </c>
       <c r="V25" t="n">
-        <v>-0.3856</v>
+        <v>-0.387</v>
       </c>
       <c r="W25" t="n">
-        <v>1.2534</v>
+        <v>1.2472</v>
       </c>
       <c r="X25" t="n">
-        <v>-1.639</v>
+        <v>-1.6342</v>
       </c>
     </row>
     <row r="26">
@@ -2437,67 +2437,67 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-3.783</v>
+        <v>-2.976400000000001</v>
       </c>
       <c r="E26" t="n">
-        <v>2.155199999999999</v>
+        <v>1.860300000000001</v>
       </c>
       <c r="F26" t="n">
-        <v>-5.938</v>
+        <v>-4.8367</v>
       </c>
       <c r="G26" t="n">
-        <v>-11.4746</v>
+        <v>-11.4677</v>
       </c>
       <c r="H26" t="n">
-        <v>-1.6522</v>
+        <v>-1.6515</v>
       </c>
       <c r="I26" t="n">
-        <v>-9.822499999999998</v>
+        <v>-9.8163</v>
       </c>
       <c r="J26" t="n">
-        <v>6.586800000000002</v>
+        <v>6.355900000000001</v>
       </c>
       <c r="K26" t="n">
-        <v>6.3076</v>
+        <v>6.181799999999999</v>
       </c>
       <c r="L26" t="n">
-        <v>0.2791000000000001</v>
+        <v>0.1741000000000004</v>
       </c>
       <c r="M26" t="n">
-        <v>-18.0614</v>
+        <v>-17.8236</v>
       </c>
       <c r="N26" t="n">
-        <v>-7.959899999999999</v>
+        <v>-7.833299999999999</v>
       </c>
       <c r="O26" t="n">
-        <v>-10.1015</v>
+        <v>-9.9903</v>
       </c>
       <c r="P26" t="n">
-        <v>6.661338147750939e-16</v>
+        <v>1.665334536937735e-16</v>
       </c>
       <c r="Q26" t="n">
-        <v>-17.0125</v>
+        <v>-17.0724</v>
       </c>
       <c r="R26" t="n">
-        <v>17.0126</v>
+        <v>17.0725</v>
       </c>
       <c r="S26" t="n">
-        <v>4.188800000000001</v>
+        <v>4.9937</v>
       </c>
       <c r="T26" t="n">
-        <v>3.3572</v>
+        <v>3.3877</v>
       </c>
       <c r="U26" t="n">
-        <v>0.8316000000000001</v>
+        <v>1.6061</v>
       </c>
       <c r="V26" t="n">
-        <v>3.503</v>
+        <v>3.4976</v>
       </c>
       <c r="W26" t="n">
-        <v>9.223600000000001</v>
+        <v>9.1891</v>
       </c>
       <c r="X26" t="n">
-        <v>-5.7206</v>
+        <v>-5.6915</v>
       </c>
     </row>
   </sheetData>

--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104706_W28.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104706_W28.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X26"/>
+  <dimension ref="A1:Y26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,6 +549,11 @@
           <t>Def_FT</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Game_File</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -627,6 +632,11 @@
       <c r="X2" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>play_by_play_104706_W28.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -705,6 +715,11 @@
       <c r="X3" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>play_by_play_104706_W28.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -783,6 +798,11 @@
       <c r="X4" t="n">
         <v>-0.5447</v>
       </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>play_by_play_104706_W28.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -861,6 +881,11 @@
       <c r="X5" t="n">
         <v>0</v>
       </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>play_by_play_104706_W28.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -939,6 +964,11 @@
       <c r="X6" t="n">
         <v>-0.7025</v>
       </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>play_by_play_104706_W28.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1017,6 +1047,11 @@
       <c r="X7" t="n">
         <v>0</v>
       </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>play_by_play_104706_W28.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1095,6 +1130,11 @@
       <c r="X8" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>play_by_play_104706_W28.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1173,6 +1213,11 @@
       <c r="X9" t="n">
         <v>0</v>
       </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>play_by_play_104706_W28.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1251,6 +1296,11 @@
       <c r="X10" t="n">
         <v>0</v>
       </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>play_by_play_104706_W28.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1329,6 +1379,11 @@
       <c r="X11" t="n">
         <v>-1.2472</v>
       </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>play_by_play_104706_W28.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1407,6 +1462,11 @@
       <c r="X12" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>play_by_play_104706_W28.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1485,6 +1545,11 @@
       <c r="X13" t="n">
         <v>-2.1789</v>
       </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>play_by_play_104706_W28.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1563,6 +1628,7 @@
       <c r="X14" t="n">
         <v>-8.099600000000001</v>
       </c>
+      <c r="Y14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1641,6 +1707,11 @@
       <c r="X15" t="n">
         <v>0</v>
       </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>play_by_play_104706_W28.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1719,6 +1790,11 @@
       <c r="X16" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>play_by_play_104706_W28.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1797,6 +1873,11 @@
       <c r="X17" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>play_by_play_104706_W28.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1875,6 +1956,11 @@
       <c r="X18" t="n">
         <v>0</v>
       </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>play_by_play_104706_W28.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1953,6 +2039,11 @@
       <c r="X19" t="n">
         <v>0.07140000000000001</v>
       </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>play_by_play_104706_W28.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2031,6 +2122,11 @@
       <c r="X20" t="n">
         <v>-0.7025</v>
       </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>play_by_play_104706_W28.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2109,6 +2205,11 @@
       <c r="X21" t="n">
         <v>0</v>
       </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>play_by_play_104706_W28.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2187,6 +2288,11 @@
       <c r="X22" t="n">
         <v>0</v>
       </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>play_by_play_104706_W28.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2265,6 +2371,11 @@
       <c r="X23" t="n">
         <v>-2.1789</v>
       </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>play_by_play_104706_W28.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2343,6 +2454,11 @@
       <c r="X24" t="n">
         <v>0</v>
       </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>play_by_play_104706_W28.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2421,6 +2537,11 @@
       <c r="X25" t="n">
         <v>-1.6342</v>
       </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>play_by_play_104706_W28.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -2499,6 +2620,7 @@
       <c r="X26" t="n">
         <v>-5.6915</v>
       </c>
+      <c r="Y26" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
